--- a/연구(근대,현대).xlsx
+++ b/연구(근대,현대).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA21CCC-4E2F-4E05-ABBC-C1F5FD7F0E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67D9858-1029-4472-A6EC-E40164A6B86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19785" windowHeight="20880" xr2:uid="{2BE2D191-3B93-441E-8877-55C8BC94D2C0}"/>
+    <workbookView xWindow="17745" yWindow="45" windowWidth="28620" windowHeight="20880" xr2:uid="{2BE2D191-3B93-441E-8877-55C8BC94D2C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="831">
   <si>
     <t>id</t>
   </si>
@@ -1897,15 +1897,6 @@
   </si>
   <si>
     <t>장용영</t>
-  </si>
-  <si>
-    <t>1d 00:48:58</t>
-  </si>
-  <si>
-    <t>1d 04:21:41</t>
-  </si>
-  <si>
-    <t>1d 14:24:22</t>
   </si>
   <si>
     <t>정약용 등용</t>
@@ -3382,19 +3373,17 @@
   <dimension ref="A1:AC301"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="7"/>
     <col min="5" max="5" width="25.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" style="7" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="15" width="8.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="12.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="12.75" style="7" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.875" style="7" bestFit="1" customWidth="1"/>
     <col min="29" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -3403,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -3483,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>25</v>
@@ -3563,7 +3552,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>28</v>
@@ -3643,7 +3632,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>33</v>
@@ -3723,7 +3712,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>38</v>
@@ -3803,7 +3792,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>40</v>
@@ -3883,7 +3872,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>42</v>
@@ -3963,7 +3952,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>45</v>
@@ -4043,7 +4032,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>52</v>
@@ -4123,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>54</v>
@@ -4203,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>56</v>
@@ -4283,7 +4272,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>62</v>
@@ -4363,7 +4352,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>64</v>
@@ -4443,7 +4432,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>66</v>
@@ -4523,7 +4512,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>68</v>
@@ -4532,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="F15" s="7">
         <v>0</v>
@@ -4603,7 +4592,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>70</v>
@@ -4683,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>72</v>
@@ -4763,7 +4752,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>78</v>
@@ -4843,7 +4832,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>80</v>
@@ -4923,7 +4912,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>92</v>
@@ -5003,7 +4992,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>94</v>
@@ -5083,16 +5072,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D22" s="15">
         <v>10</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="F22" s="7">
         <v>0</v>
@@ -5163,7 +5152,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>97</v>
@@ -5243,7 +5232,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>99</v>
@@ -5323,7 +5312,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C25" s="22" t="s">
         <v>104</v>
@@ -5403,7 +5392,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>106</v>
@@ -5412,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="F26" s="7">
         <v>1</v>
@@ -5483,7 +5472,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>108</v>
@@ -5563,7 +5552,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>110</v>
@@ -5643,7 +5632,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>121</v>
@@ -5723,7 +5712,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>122</v>
@@ -5803,7 +5792,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>133</v>
@@ -5883,7 +5872,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C32" s="21" t="s">
         <v>134</v>
@@ -5963,7 +5952,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>135</v>
@@ -6043,7 +6032,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>137</v>
@@ -6123,7 +6112,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>138</v>
@@ -6203,7 +6192,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>150</v>
@@ -6283,7 +6272,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C37" s="22" t="s">
         <v>160</v>
@@ -6363,7 +6352,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C38" s="22" t="s">
         <v>171</v>
@@ -6443,7 +6432,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>172</v>
@@ -6523,7 +6512,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>183</v>
@@ -6603,7 +6592,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>185</v>
@@ -6683,7 +6672,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>191</v>
@@ -6763,7 +6752,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>197</v>
@@ -6843,7 +6832,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>198</v>
@@ -6923,7 +6912,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>199</v>
@@ -7003,7 +6992,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>200</v>
@@ -7083,7 +7072,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>133</v>
@@ -7163,7 +7152,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>201</v>
@@ -7243,7 +7232,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>209</v>
@@ -7323,7 +7312,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>210</v>
@@ -7403,7 +7392,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>211</v>
@@ -7483,7 +7472,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>217</v>
@@ -7563,7 +7552,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>218</v>
@@ -7643,7 +7632,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>219</v>
@@ -7723,7 +7712,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>230</v>
@@ -7803,7 +7792,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>231</v>
@@ -7883,7 +7872,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>232</v>
@@ -7963,7 +7952,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>233</v>
@@ -8043,7 +8032,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>237</v>
@@ -8123,7 +8112,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>238</v>
@@ -8203,7 +8192,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>239</v>
@@ -8283,7 +8272,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>240</v>
@@ -8363,7 +8352,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>246</v>
@@ -8443,7 +8432,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>252</v>
@@ -8523,7 +8512,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>261</v>
@@ -8600,7 +8589,7 @@
     </row>
     <row r="66" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="28" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.3">
@@ -8608,7 +8597,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>262</v>
@@ -8688,7 +8677,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>264</v>
@@ -8768,7 +8757,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>269</v>
@@ -8848,7 +8837,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>271</v>
@@ -8928,7 +8917,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>273</v>
@@ -9008,7 +8997,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>277</v>
@@ -9088,7 +9077,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>279</v>
@@ -9168,7 +9157,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>290</v>
@@ -9248,7 +9237,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>291</v>
@@ -9328,7 +9317,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>292</v>
@@ -9408,7 +9397,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>293</v>
@@ -9488,7 +9477,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>301</v>
@@ -9568,7 +9557,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>302</v>
@@ -9648,7 +9637,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>303</v>
@@ -9728,7 +9717,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>311</v>
@@ -9808,7 +9797,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>322</v>
@@ -9888,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>333</v>
@@ -9968,7 +9957,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>334</v>
@@ -10048,7 +10037,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>335</v>
@@ -10128,7 +10117,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>337</v>
@@ -10208,16 +10197,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D87" s="6">
         <v>3</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F87" s="7">
         <v>0</v>
@@ -10288,7 +10277,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>340</v>
@@ -10368,7 +10357,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>341</v>
@@ -10448,7 +10437,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>343</v>
@@ -10528,7 +10517,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>351</v>
@@ -10608,7 +10597,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>357</v>
@@ -10688,7 +10677,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>359</v>
@@ -10768,7 +10757,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>364</v>
@@ -10848,7 +10837,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>365</v>
@@ -10928,7 +10917,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>366</v>
@@ -11008,7 +10997,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>367</v>
@@ -11088,7 +11077,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>370</v>
@@ -11168,7 +11157,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>372</v>
@@ -11248,10 +11237,10 @@
         <v>98</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D100" s="6">
         <v>10</v>
@@ -11328,7 +11317,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>373</v>
@@ -11408,7 +11397,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>374</v>
@@ -11488,7 +11477,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>380</v>
@@ -11568,7 +11557,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>381</v>
@@ -11648,7 +11637,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>382</v>
@@ -11728,7 +11717,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>383</v>
@@ -11808,7 +11797,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>384</v>
@@ -11888,7 +11877,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>385</v>
@@ -11968,7 +11957,7 @@
         <v>107</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>386</v>
@@ -12048,7 +12037,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>387</v>
@@ -12128,7 +12117,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>388</v>
@@ -12208,7 +12197,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>389</v>
@@ -12288,7 +12277,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>391</v>
@@ -12368,7 +12357,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>396</v>
@@ -12448,7 +12437,7 @@
         <v>113</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>404</v>
@@ -12528,7 +12517,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>405</v>
@@ -12605,7 +12594,7 @@
     </row>
     <row r="117" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="28" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.3">
@@ -12613,7 +12602,7 @@
         <v>115</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>408</v>
@@ -12693,7 +12682,7 @@
         <v>116</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>412</v>
@@ -12773,7 +12762,7 @@
         <v>117</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>423</v>
@@ -12853,7 +12842,7 @@
         <v>118</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>424</v>
@@ -12933,7 +12922,7 @@
         <v>119</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>425</v>
@@ -13013,7 +13002,7 @@
         <v>120</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>427</v>
@@ -13093,7 +13082,7 @@
         <v>121</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>433</v>
@@ -13173,7 +13162,7 @@
         <v>122</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>439</v>
@@ -13253,7 +13242,7 @@
         <v>123</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>441</v>
@@ -13333,7 +13322,7 @@
         <v>124</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>451</v>
@@ -13413,7 +13402,7 @@
         <v>125</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>462</v>
@@ -13493,7 +13482,7 @@
         <v>126</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>473</v>
@@ -13573,7 +13562,7 @@
         <v>127</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>484</v>
@@ -13653,7 +13642,7 @@
         <v>128</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>493</v>
@@ -13733,7 +13722,7 @@
         <v>129</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>494</v>
@@ -13813,7 +13802,7 @@
         <v>130</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>496</v>
@@ -13893,7 +13882,7 @@
         <v>131</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>498</v>
@@ -13973,7 +13962,7 @@
         <v>132</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>501</v>
@@ -14053,7 +14042,7 @@
         <v>133</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>511</v>
@@ -14133,7 +14122,7 @@
         <v>134</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>513</v>
@@ -14213,7 +14202,7 @@
         <v>135</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>515</v>
@@ -14293,7 +14282,7 @@
         <v>136</v>
       </c>
       <c r="B139" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C139" s="24" t="s">
         <v>519</v>
@@ -14373,7 +14362,7 @@
         <v>137</v>
       </c>
       <c r="B140" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C140" s="24" t="s">
         <v>527</v>
@@ -14453,7 +14442,7 @@
         <v>138</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C141" s="23" t="s">
         <v>528</v>
@@ -14533,7 +14522,7 @@
         <v>139</v>
       </c>
       <c r="B142" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C142" s="24" t="s">
         <v>530</v>
@@ -14613,7 +14602,7 @@
         <v>140</v>
       </c>
       <c r="B143" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C143" s="24" t="s">
         <v>535</v>
@@ -14693,7 +14682,7 @@
         <v>141</v>
       </c>
       <c r="B144" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C144" s="24" t="s">
         <v>536</v>
@@ -14773,7 +14762,7 @@
         <v>142</v>
       </c>
       <c r="B145" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C145" s="24" t="s">
         <v>537</v>
@@ -14853,7 +14842,7 @@
         <v>143</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C146" s="23" t="s">
         <v>538</v>
@@ -14933,7 +14922,7 @@
         <v>144</v>
       </c>
       <c r="B147" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C147" s="24" t="s">
         <v>542</v>
@@ -15013,7 +15002,7 @@
         <v>145</v>
       </c>
       <c r="B148" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C148" s="24" t="s">
         <v>549</v>
@@ -15093,7 +15082,7 @@
         <v>146</v>
       </c>
       <c r="B149" s="24" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C149" s="24" t="s">
         <v>550</v>
@@ -15173,7 +15162,7 @@
         <v>147</v>
       </c>
       <c r="B150" s="23" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C150" s="23" t="s">
         <v>551</v>
@@ -15253,7 +15242,7 @@
         <v>148</v>
       </c>
       <c r="B151" s="23" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C151" s="23" t="s">
         <v>559</v>
@@ -15333,7 +15322,7 @@
         <v>149</v>
       </c>
       <c r="B152" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C152" s="22" t="s">
         <v>560</v>
@@ -15413,7 +15402,7 @@
         <v>150</v>
       </c>
       <c r="B153" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C153" s="25" t="s">
         <v>566</v>
@@ -15493,7 +15482,7 @@
         <v>151</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C154" s="25" t="s">
         <v>574</v>
@@ -15573,7 +15562,7 @@
         <v>152</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C155" s="25" t="s">
         <v>575</v>
@@ -15653,7 +15642,7 @@
         <v>153</v>
       </c>
       <c r="B156" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C156" s="22" t="s">
         <v>576</v>
@@ -15733,7 +15722,7 @@
         <v>154</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>580</v>
@@ -15813,7 +15802,7 @@
         <v>155</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C158" s="25" t="s">
         <v>586</v>
@@ -15893,7 +15882,7 @@
         <v>156</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C159" s="22" t="s">
         <v>587</v>
@@ -15973,7 +15962,7 @@
         <v>157</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C160" s="25" t="s">
         <v>588</v>
@@ -16053,7 +16042,7 @@
         <v>158</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C161" s="25" t="s">
         <v>598</v>
@@ -16133,7 +16122,7 @@
         <v>159</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C162" s="25" t="s">
         <v>599</v>
@@ -16213,7 +16202,7 @@
         <v>160</v>
       </c>
       <c r="B163" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C163" s="25" t="s">
         <v>600</v>
@@ -16293,7 +16282,7 @@
         <v>161</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C164" s="25" t="s">
         <v>601</v>
@@ -16373,7 +16362,7 @@
         <v>162</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C165" s="22" t="s">
         <v>602</v>
@@ -16453,7 +16442,7 @@
         <v>163</v>
       </c>
       <c r="B166" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C166" s="25" t="s">
         <v>608</v>
@@ -16533,7 +16522,7 @@
         <v>164</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C167" s="25" t="s">
         <v>619</v>
@@ -16599,13 +16588,13 @@
         <v>615</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="Y167" s="7" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="Z167" s="7" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="168" spans="1:29" x14ac:dyDescent="0.3">
@@ -16613,10 +16602,10 @@
         <v>165</v>
       </c>
       <c r="B168" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D168" s="25">
         <v>10</v>
@@ -16693,10 +16682,10 @@
         <v>166</v>
       </c>
       <c r="B169" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D169" s="25">
         <v>10</v>
@@ -16773,10 +16762,10 @@
         <v>167</v>
       </c>
       <c r="B170" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D170" s="25">
         <v>10</v>
@@ -16853,10 +16842,10 @@
         <v>168</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D171" s="22">
         <v>3</v>
@@ -16898,13 +16887,13 @@
         <v>-1</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="R171" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="S171" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="T171" s="7">
         <v>-1</v>
@@ -16933,16 +16922,16 @@
         <v>169</v>
       </c>
       <c r="B172" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C172" s="25" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D172" s="25">
         <v>10</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="F172" s="7">
         <v>1</v>
@@ -16978,34 +16967,34 @@
         <v>10</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="R172" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="S172" s="7" t="s">
         <v>401</v>
       </c>
       <c r="T172" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="U172" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="V172" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="W172" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="U172" s="7" t="s">
+      <c r="X172" s="7" t="s">
         <v>634</v>
       </c>
-      <c r="V172" s="7" t="s">
+      <c r="Y172" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="W172" s="7" t="s">
+      <c r="Z172" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="X172" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="Y172" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="Z172" s="7" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="173" spans="1:29" x14ac:dyDescent="0.3">
@@ -17013,10 +17002,10 @@
         <v>170</v>
       </c>
       <c r="B173" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D173" s="25">
         <v>10</v>
@@ -17058,34 +17047,34 @@
         <v>10</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="R173" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="S173" s="7" t="s">
         <v>401</v>
       </c>
       <c r="T173" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="U173" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="V173" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="W173" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="U173" s="7" t="s">
+      <c r="X173" s="7" t="s">
         <v>634</v>
       </c>
-      <c r="V173" s="7" t="s">
+      <c r="Y173" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="W173" s="7" t="s">
+      <c r="Z173" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="X173" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="Y173" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="Z173" s="7" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="174" spans="1:29" x14ac:dyDescent="0.3">
@@ -17093,10 +17082,10 @@
         <v>171</v>
       </c>
       <c r="B174" s="25" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D174" s="25">
         <v>10</v>
@@ -17138,48 +17127,48 @@
         <v>10</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="R174" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="S174" s="7" t="s">
         <v>401</v>
       </c>
       <c r="T174" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="U174" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="V174" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="W174" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="U174" s="7" t="s">
+      <c r="X174" s="7" t="s">
         <v>634</v>
       </c>
-      <c r="V174" s="7" t="s">
+      <c r="Y174" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="W174" s="7" t="s">
+      <c r="Z174" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="X174" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="Y174" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="Z174" s="7" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="175" spans="1:29" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="28" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AA175" s="33" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="AB175" s="28" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="AC175" s="28" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="176" spans="1:29" x14ac:dyDescent="0.3">
@@ -17187,16 +17176,16 @@
         <v>172</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D176" s="1">
         <v>10</v>
       </c>
       <c r="E176" s="47" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F176" s="8">
         <v>0</v>
@@ -17232,34 +17221,34 @@
         <v>10</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="S176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="T176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="U176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="V176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="W176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="X176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="Y176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="Z176" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AA176" s="1">
         <v>250000</v>
@@ -17277,10 +17266,10 @@
         <v>173</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D177" s="2">
         <v>5</v>
@@ -17322,19 +17311,19 @@
         <v>-1</v>
       </c>
       <c r="Q177" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="R177" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="S177" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="T177" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="U177" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="V177" s="7">
         <v>-1</v>
@@ -17367,10 +17356,10 @@
         <v>174</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D178" s="2">
         <v>5</v>
@@ -17412,19 +17401,19 @@
         <v>-1</v>
       </c>
       <c r="Q178" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="R178" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="S178" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="T178" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="U178" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="V178" s="7">
         <v>-1</v>
@@ -17457,10 +17446,10 @@
         <v>175</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D179" s="2">
         <v>5</v>
@@ -17502,19 +17491,19 @@
         <v>-1</v>
       </c>
       <c r="Q179" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="T179" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="U179" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="V179" s="7">
         <v>-1</v>
@@ -17547,10 +17536,10 @@
         <v>176</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D180" s="2">
         <v>5</v>
@@ -17592,19 +17581,19 @@
         <v>-1</v>
       </c>
       <c r="Q180" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="R180" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="S180" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="T180" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="U180" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="V180" s="7">
         <v>-1</v>
@@ -17637,10 +17626,10 @@
         <v>177</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D181" s="2">
         <v>5</v>
@@ -17682,19 +17671,19 @@
         <v>-1</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="S181" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="T181" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="U181" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="V181" s="7">
         <v>-1</v>
@@ -17727,10 +17716,10 @@
         <v>178</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D182" s="2">
         <v>5</v>
@@ -17772,19 +17761,19 @@
         <v>-1</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="R182" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="S182" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="T182" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="U182" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="V182" s="7">
         <v>-1</v>
@@ -17817,16 +17806,16 @@
         <v>179</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D183" s="1">
         <v>10</v>
       </c>
       <c r="E183" s="47" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F183" s="8">
         <v>0</v>
@@ -17862,34 +17851,34 @@
         <v>20</v>
       </c>
       <c r="Q183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="R183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="S183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="T183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="U183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="V183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="W183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="X183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="Y183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="Z183" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="AA183" s="1">
         <v>280000</v>
@@ -17907,16 +17896,16 @@
         <v>180</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D184" s="2">
         <v>5</v>
       </c>
       <c r="E184" s="51" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F184" s="9">
         <v>0</v>
@@ -17952,19 +17941,19 @@
         <v>-1</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="R184" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="S184" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="T184" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="U184" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="V184" s="7">
         <v>-1</v>
@@ -17997,16 +17986,16 @@
         <v>181</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D185" s="2">
         <v>5</v>
       </c>
       <c r="E185" s="51" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F185" s="9">
         <v>1</v>
@@ -18042,19 +18031,19 @@
         <v>-1</v>
       </c>
       <c r="Q185" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="R185" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="T185" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="U185" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="V185" s="7">
         <v>-1</v>
@@ -18087,10 +18076,10 @@
         <v>182</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D186" s="2">
         <v>5</v>
@@ -18132,19 +18121,19 @@
         <v>-1</v>
       </c>
       <c r="Q186" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="R186" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="S186" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="T186" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="U186" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="V186" s="7">
         <v>-1</v>
@@ -18177,16 +18166,16 @@
         <v>183</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D187" s="2">
         <v>5</v>
       </c>
       <c r="E187" s="51" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F187" s="9">
         <v>1</v>
@@ -18222,19 +18211,19 @@
         <v>-1</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="R187" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="S187" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="T187" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="U187" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="V187" s="7">
         <v>-1</v>
@@ -18267,10 +18256,10 @@
         <v>184</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D188" s="2">
         <v>5</v>
@@ -18312,19 +18301,19 @@
         <v>-1</v>
       </c>
       <c r="Q188" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="R188" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="S188" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="T188" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="U188" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="V188" s="7">
         <v>-1</v>
@@ -18357,10 +18346,10 @@
         <v>185</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D189" s="2">
         <v>5</v>
@@ -18402,19 +18391,19 @@
         <v>-1</v>
       </c>
       <c r="Q189" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="R189" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="S189" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="T189" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="U189" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="V189" s="7">
         <v>-1</v>
@@ -18447,16 +18436,16 @@
         <v>186</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D190" s="1">
         <v>10</v>
       </c>
       <c r="E190" s="47" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F190" s="8">
         <v>0</v>
@@ -18492,34 +18481,34 @@
         <v>50</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="S190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="T190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="U190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="V190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="W190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="X190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Z190" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="AA190" s="1">
         <v>310000</v>
@@ -18537,10 +18526,10 @@
         <v>187</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D191" s="2">
         <v>5</v>
@@ -18582,19 +18571,19 @@
         <v>-1</v>
       </c>
       <c r="Q191" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="R191" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S191" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="T191" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="U191" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="V191" s="7">
         <v>-1</v>
@@ -18627,10 +18616,10 @@
         <v>188</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D192" s="2">
         <v>5</v>
@@ -18672,19 +18661,19 @@
         <v>-1</v>
       </c>
       <c r="Q192" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="R192" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S192" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="T192" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="U192" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="V192" s="7">
         <v>-1</v>
@@ -18717,10 +18706,10 @@
         <v>189</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D193" s="2">
         <v>5</v>
@@ -18762,19 +18751,19 @@
         <v>-1</v>
       </c>
       <c r="Q193" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="R193" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S193" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="T193" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="U193" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="V193" s="7">
         <v>-1</v>
@@ -18807,16 +18796,16 @@
         <v>190</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D194" s="1">
         <v>10</v>
       </c>
       <c r="E194" s="47" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F194" s="8">
         <v>0</v>
@@ -18852,34 +18841,34 @@
         <v>20</v>
       </c>
       <c r="Q194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="R194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="S194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="T194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="U194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="V194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="W194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="X194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="Y194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="Z194" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="AA194" s="1">
         <v>330000</v>
@@ -18897,16 +18886,16 @@
         <v>191</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D195" s="3">
         <v>10</v>
       </c>
       <c r="E195" s="48" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F195" s="10">
         <v>0</v>
@@ -18942,34 +18931,34 @@
         <v>60</v>
       </c>
       <c r="Q195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="R195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="S195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="T195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="U195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="V195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="W195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="X195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="Y195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="Z195" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="AA195" s="3">
         <v>340000</v>
@@ -18987,10 +18976,10 @@
         <v>192</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D196" s="4">
         <v>3</v>
@@ -19032,13 +19021,13 @@
         <v>-1</v>
       </c>
       <c r="Q196" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R196" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S196" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T196" s="7">
         <v>-1</v>
@@ -19077,10 +19066,10 @@
         <v>193</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D197" s="4">
         <v>3</v>
@@ -19122,13 +19111,13 @@
         <v>-1</v>
       </c>
       <c r="Q197" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R197" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S197" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T197" s="7">
         <v>-1</v>
@@ -19167,10 +19156,10 @@
         <v>194</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D198" s="4">
         <v>3</v>
@@ -19212,13 +19201,13 @@
         <v>-1</v>
       </c>
       <c r="Q198" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R198" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S198" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T198" s="7">
         <v>-1</v>
@@ -19257,10 +19246,10 @@
         <v>195</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D199" s="4">
         <v>3</v>
@@ -19302,13 +19291,13 @@
         <v>-1</v>
       </c>
       <c r="Q199" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R199" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S199" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T199" s="7">
         <v>-1</v>
@@ -19347,16 +19336,16 @@
         <v>196</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D200" s="3">
         <v>10</v>
       </c>
       <c r="E200" s="48" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F200" s="10">
         <v>0</v>
@@ -19392,34 +19381,34 @@
         <v>45</v>
       </c>
       <c r="Q200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="R200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="S200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="T200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="U200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="V200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="W200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="X200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="Y200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="Z200" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AA200" s="3">
         <v>360000</v>
@@ -19437,10 +19426,10 @@
         <v>197</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D201" s="4">
         <v>3</v>
@@ -19482,13 +19471,13 @@
         <v>-1</v>
       </c>
       <c r="Q201" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="R201" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="S201" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="T201" s="7">
         <v>-1</v>
@@ -19527,10 +19516,10 @@
         <v>198</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D202" s="4">
         <v>3</v>
@@ -19572,13 +19561,13 @@
         <v>-1</v>
       </c>
       <c r="Q202" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="R202" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="S202" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="T202" s="7">
         <v>-1</v>
@@ -19617,10 +19606,10 @@
         <v>199</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D203" s="4">
         <v>3</v>
@@ -19662,13 +19651,13 @@
         <v>-1</v>
       </c>
       <c r="Q203" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="R203" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="S203" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="T203" s="7">
         <v>-1</v>
@@ -19707,10 +19696,10 @@
         <v>200</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D204" s="4">
         <v>3</v>
@@ -19752,13 +19741,13 @@
         <v>-1</v>
       </c>
       <c r="Q204" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="R204" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="S204" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="T204" s="7">
         <v>-1</v>
@@ -19797,10 +19786,10 @@
         <v>201</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D205" s="4">
         <v>5</v>
@@ -19842,19 +19831,19 @@
         <v>-1</v>
       </c>
       <c r="Q205" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="R205" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="S205" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="T205" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="U205" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="V205" s="7">
         <v>-1</v>
@@ -19887,10 +19876,10 @@
         <v>202</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D206" s="4">
         <v>5</v>
@@ -19932,19 +19921,19 @@
         <v>-1</v>
       </c>
       <c r="Q206" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="R206" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="S206" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="T206" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="U206" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="V206" s="7">
         <v>-1</v>
@@ -19977,10 +19966,10 @@
         <v>203</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D207" s="4">
         <v>5</v>
@@ -20022,19 +20011,19 @@
         <v>-1</v>
       </c>
       <c r="Q207" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="R207" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="S207" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="T207" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="U207" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="V207" s="7">
         <v>-1</v>
@@ -20067,16 +20056,16 @@
         <v>204</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D208" s="3">
         <v>10</v>
       </c>
       <c r="E208" s="48" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F208" s="10">
         <v>0</v>
@@ -20112,34 +20101,34 @@
         <v>65</v>
       </c>
       <c r="Q208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="R208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="S208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="T208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="U208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="V208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="W208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="X208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="Y208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="Z208" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="AA208" s="3">
         <v>390000</v>
@@ -20157,10 +20146,10 @@
         <v>205</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D209" s="4">
         <v>5</v>
@@ -20202,19 +20191,19 @@
         <v>-1</v>
       </c>
       <c r="Q209" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="R209" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="S209" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="T209" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="U209" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="V209" s="7">
         <v>-1</v>
@@ -20247,10 +20236,10 @@
         <v>206</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D210" s="4">
         <v>5</v>
@@ -20292,19 +20281,19 @@
         <v>-1</v>
       </c>
       <c r="Q210" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="R210" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="S210" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="T210" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="U210" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="V210" s="7">
         <v>-1</v>
@@ -20337,10 +20326,10 @@
         <v>207</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D211" s="4">
         <v>5</v>
@@ -20382,19 +20371,19 @@
         <v>-1</v>
       </c>
       <c r="Q211" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="R211" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="S211" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="T211" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="U211" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="V211" s="7">
         <v>-1</v>
@@ -20427,10 +20416,10 @@
         <v>208</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D212" s="4">
         <v>5</v>
@@ -20472,19 +20461,19 @@
         <v>-1</v>
       </c>
       <c r="Q212" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="R212" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="S212" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="T212" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="U212" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="V212" s="7">
         <v>-1</v>
@@ -20517,10 +20506,10 @@
         <v>209</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D213" s="4">
         <v>5</v>
@@ -20562,19 +20551,19 @@
         <v>-1</v>
       </c>
       <c r="Q213" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="R213" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="S213" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="T213" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="U213" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="V213" s="7">
         <v>-1</v>
@@ -20607,10 +20596,10 @@
         <v>210</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D214" s="4">
         <v>5</v>
@@ -20652,19 +20641,19 @@
         <v>-1</v>
       </c>
       <c r="Q214" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="R214" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="S214" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="T214" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="U214" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="V214" s="7">
         <v>-1</v>
@@ -20697,16 +20686,16 @@
         <v>211</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D215" s="5">
         <v>10</v>
       </c>
       <c r="E215" s="56" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F215" s="12">
         <v>0</v>
@@ -20742,34 +20731,34 @@
         <v>100</v>
       </c>
       <c r="Q215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="R215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="S215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="T215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="U215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="V215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="W215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="X215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="Y215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="Z215" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="AA215" s="5">
         <v>420000</v>
@@ -20787,16 +20776,16 @@
         <v>212</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D216" s="6">
         <v>7</v>
       </c>
       <c r="E216" s="54" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F216" s="13">
         <v>0</v>
@@ -20832,25 +20821,25 @@
         <v>-1</v>
       </c>
       <c r="Q216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="R216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="S216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="T216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="U216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="V216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="W216" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="X216" s="7">
         <v>-1</v>
@@ -20877,16 +20866,16 @@
         <v>213</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D217" s="6">
         <v>7</v>
       </c>
       <c r="E217" s="54" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F217" s="13">
         <v>1</v>
@@ -20922,25 +20911,25 @@
         <v>-1</v>
       </c>
       <c r="Q217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="R217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="S217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="T217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="U217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="V217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="W217" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="X217" s="7">
         <v>-1</v>
@@ -20967,10 +20956,10 @@
         <v>214</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D218" s="6">
         <v>7</v>
@@ -21012,25 +21001,25 @@
         <v>-1</v>
       </c>
       <c r="Q218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="R218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="S218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="T218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="U218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="V218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="W218" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="X218" s="7">
         <v>-1</v>
@@ -21057,10 +21046,10 @@
         <v>215</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D219" s="6">
         <v>7</v>
@@ -21102,25 +21091,25 @@
         <v>-1</v>
       </c>
       <c r="Q219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="R219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="S219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="T219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="U219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="V219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="W219" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="X219" s="7">
         <v>-1</v>
@@ -21147,10 +21136,10 @@
         <v>216</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D220" s="6">
         <v>7</v>
@@ -21192,25 +21181,25 @@
         <v>-1</v>
       </c>
       <c r="Q220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="R220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="S220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="T220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="U220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="V220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="W220" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="X220" s="7">
         <v>-1</v>
@@ -21237,10 +21226,10 @@
         <v>217</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D221" s="6">
         <v>7</v>
@@ -21282,25 +21271,25 @@
         <v>-1</v>
       </c>
       <c r="Q221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="R221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="S221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="T221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="U221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="V221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="W221" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="X221" s="7">
         <v>-1</v>
@@ -21327,10 +21316,10 @@
         <v>218</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D222" s="6">
         <v>3</v>
@@ -21372,13 +21361,13 @@
         <v>-1</v>
       </c>
       <c r="Q222" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="R222" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="S222" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="T222" s="7">
         <v>-1</v>
@@ -21417,10 +21406,10 @@
         <v>219</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D223" s="6">
         <v>3</v>
@@ -21462,13 +21451,13 @@
         <v>-1</v>
       </c>
       <c r="Q223" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="R223" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="S223" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="T223" s="7">
         <v>-1</v>
@@ -21507,16 +21496,16 @@
         <v>220</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D224" s="6">
         <v>3</v>
       </c>
       <c r="E224" s="54" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F224" s="13">
         <v>1</v>
@@ -21552,13 +21541,13 @@
         <v>-1</v>
       </c>
       <c r="Q224" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="R224" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="S224" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="T224" s="7">
         <v>-1</v>
@@ -21597,10 +21586,10 @@
         <v>221</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D225" s="6">
         <v>3</v>
@@ -21642,13 +21631,13 @@
         <v>-1</v>
       </c>
       <c r="Q225" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="R225" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="S225" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="T225" s="7">
         <v>-1</v>
@@ -21687,16 +21676,16 @@
         <v>222</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D226" s="5">
         <v>10</v>
       </c>
       <c r="E226" s="56" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F226" s="12">
         <v>0</v>
@@ -21732,34 +21721,34 @@
         <v>170</v>
       </c>
       <c r="Q226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="R226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="S226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="T226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="U226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="V226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="W226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="X226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="Y226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="Z226" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="AA226" s="5">
         <v>470000</v>
@@ -21777,10 +21766,10 @@
         <v>223</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D227" s="6">
         <v>5</v>
@@ -21822,19 +21811,19 @@
         <v>-1</v>
       </c>
       <c r="Q227" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="R227" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="S227" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="T227" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="U227" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="V227" s="7">
         <v>-1</v>
@@ -21867,10 +21856,10 @@
         <v>224</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D228" s="6">
         <v>5</v>
@@ -21912,19 +21901,19 @@
         <v>-1</v>
       </c>
       <c r="Q228" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="R228" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="S228" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="T228" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="U228" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="V228" s="7">
         <v>-1</v>
@@ -21957,10 +21946,10 @@
         <v>225</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D229" s="6">
         <v>5</v>
@@ -22002,19 +21991,19 @@
         <v>-1</v>
       </c>
       <c r="Q229" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="R229" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="S229" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="T229" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="U229" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="V229" s="7">
         <v>-1</v>
@@ -22047,16 +22036,16 @@
         <v>226</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D230" s="6">
         <v>5</v>
       </c>
       <c r="E230" s="54" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F230" s="13">
         <v>1</v>
@@ -22092,19 +22081,19 @@
         <v>-1</v>
       </c>
       <c r="Q230" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="R230" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="S230" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="T230" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="U230" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="V230" s="7">
         <v>-1</v>
@@ -22137,10 +22126,10 @@
         <v>227</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D231" s="6">
         <v>5</v>
@@ -22182,19 +22171,19 @@
         <v>-1</v>
       </c>
       <c r="Q231" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="R231" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="S231" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="T231" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="U231" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="V231" s="7">
         <v>-1</v>
@@ -22227,10 +22216,10 @@
         <v>228</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D232" s="6">
         <v>5</v>
@@ -22272,19 +22261,19 @@
         <v>-1</v>
       </c>
       <c r="Q232" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="R232" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="S232" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="T232" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="U232" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="V232" s="7">
         <v>-1</v>
@@ -22317,16 +22306,16 @@
         <v>229</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D233" s="5">
         <v>10</v>
       </c>
       <c r="E233" s="56" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F233" s="12">
         <v>0</v>
@@ -22362,34 +22351,34 @@
         <v>160</v>
       </c>
       <c r="Q233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="R233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="S233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="T233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="U233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="V233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="W233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="X233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="Y233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="Z233" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="AA233" s="5">
         <v>500000</v>
@@ -22404,7 +22393,7 @@
     </row>
     <row r="234" spans="1:29" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A234" s="28" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E234" s="44"/>
       <c r="F234" s="44"/>
@@ -22416,16 +22405,16 @@
         <v>230</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D235" s="1">
         <v>10</v>
       </c>
       <c r="E235" s="58" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F235" s="8">
         <v>1</v>
@@ -22461,34 +22450,34 @@
         <v>100</v>
       </c>
       <c r="Q235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="S235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="T235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="U235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="V235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="W235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="X235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="Y235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="Z235" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AA235" s="1">
         <v>250000</v>
@@ -22506,10 +22495,10 @@
         <v>231</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D236" s="2">
         <v>7</v>
@@ -22551,25 +22540,25 @@
         <v>-1</v>
       </c>
       <c r="Q236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="R236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="S236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="T236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="U236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="V236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="W236" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="X236" s="7">
         <v>-1</v>
@@ -22596,10 +22585,10 @@
         <v>232</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D237" s="2">
         <v>7</v>
@@ -22641,25 +22630,25 @@
         <v>-1</v>
       </c>
       <c r="Q237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="R237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="S237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="T237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="U237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="V237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="W237" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="X237" s="7">
         <v>-1</v>
@@ -22686,16 +22675,16 @@
         <v>233</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D238" s="1">
         <v>10</v>
       </c>
       <c r="E238" s="58" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F238" s="8">
         <v>0</v>
@@ -22731,34 +22720,34 @@
         <v>100</v>
       </c>
       <c r="Q238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="R238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="S238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="T238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="U238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="V238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="W238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="X238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="Y238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="Z238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AA238" s="1">
         <v>270000</v>
@@ -22776,16 +22765,16 @@
         <v>234</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D239" s="2">
         <v>5</v>
       </c>
       <c r="E239" s="65" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F239" s="9">
         <v>1</v>
@@ -22821,19 +22810,19 @@
         <v>-1</v>
       </c>
       <c r="Q239" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="R239" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="S239" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="T239" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="U239" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="V239" s="7">
         <v>-1</v>
@@ -22866,16 +22855,16 @@
         <v>235</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D240" s="2">
         <v>5</v>
       </c>
       <c r="E240" s="65" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="F240" s="9">
         <v>0</v>
@@ -22911,19 +22900,19 @@
         <v>-1</v>
       </c>
       <c r="Q240" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="R240" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="S240" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="T240" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="U240" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="V240" s="7">
         <v>-1</v>
@@ -22956,10 +22945,10 @@
         <v>236</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D241" s="2">
         <v>5</v>
@@ -23001,19 +22990,19 @@
         <v>-1</v>
       </c>
       <c r="Q241" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="R241" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="S241" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="T241" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="U241" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="V241" s="7">
         <v>-1</v>
@@ -23046,16 +23035,16 @@
         <v>237</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D242" s="1">
         <v>10</v>
       </c>
       <c r="E242" s="58" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F242" s="8">
         <v>0</v>
@@ -23091,34 +23080,34 @@
         <v>120</v>
       </c>
       <c r="Q242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="R242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="S242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="T242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="U242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="V242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="W242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="X242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="Y242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="Z242" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="AA242" s="1">
         <v>290000</v>
@@ -23136,16 +23125,16 @@
         <v>238</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D243" s="2">
         <v>5</v>
       </c>
       <c r="E243" s="65" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F243" s="9">
         <v>1</v>
@@ -23181,19 +23170,19 @@
         <v>-1</v>
       </c>
       <c r="Q243" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="R243" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="S243" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="T243" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="U243" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="V243" s="7">
         <v>-1</v>
@@ -23226,10 +23215,10 @@
         <v>239</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D244" s="2">
         <v>5</v>
@@ -23271,19 +23260,19 @@
         <v>-1</v>
       </c>
       <c r="Q244" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="R244" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="S244" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="T244" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="U244" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="V244" s="7">
         <v>-1</v>
@@ -23316,10 +23305,10 @@
         <v>240</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D245" s="2">
         <v>5</v>
@@ -23361,19 +23350,19 @@
         <v>-1</v>
       </c>
       <c r="Q245" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="R245" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="S245" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="T245" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="U245" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="V245" s="7">
         <v>-1</v>
@@ -23406,10 +23395,10 @@
         <v>241</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D246" s="1">
         <v>10</v>
@@ -23451,34 +23440,34 @@
         <v>200</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="R246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="S246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="T246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="U246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="V246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="W246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="X246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Z246" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="AA246" s="1">
         <v>310000</v>
@@ -23496,16 +23485,16 @@
         <v>242</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D247" s="1">
         <v>10</v>
       </c>
       <c r="E247" s="58" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F247" s="8">
         <v>1</v>
@@ -23541,34 +23530,34 @@
         <v>110</v>
       </c>
       <c r="Q247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="S247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="T247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="U247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="V247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="W247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="X247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="Y247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="Z247" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="AA247" s="1">
         <v>320000</v>
@@ -23586,10 +23575,10 @@
         <v>243</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D248" s="2">
         <v>3</v>
@@ -23631,13 +23620,13 @@
         <v>-1</v>
       </c>
       <c r="Q248" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="R248" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="S248" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="T248" s="7">
         <v>-1</v>
@@ -23676,10 +23665,10 @@
         <v>244</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D249" s="2">
         <v>3</v>
@@ -23721,13 +23710,13 @@
         <v>-1</v>
       </c>
       <c r="Q249" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="R249" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="S249" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="T249" s="7">
         <v>-1</v>
@@ -23766,10 +23755,10 @@
         <v>245</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D250" s="2">
         <v>3</v>
@@ -23811,13 +23800,13 @@
         <v>-1</v>
       </c>
       <c r="Q250" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="R250" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="S250" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="T250" s="7">
         <v>-1</v>
@@ -23856,10 +23845,10 @@
         <v>246</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D251" s="2">
         <v>3</v>
@@ -23901,13 +23890,13 @@
         <v>-1</v>
       </c>
       <c r="Q251" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="R251" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="S251" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="T251" s="7">
         <v>-1</v>
@@ -23946,16 +23935,16 @@
         <v>247</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D252" s="15">
         <v>10</v>
       </c>
       <c r="E252" s="59" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F252" s="16">
         <v>0</v>
@@ -23991,34 +23980,34 @@
         <v>160</v>
       </c>
       <c r="Q252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="R252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="S252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="T252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="U252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="V252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="W252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="X252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="Y252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="Z252" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="AA252" s="15">
         <v>340000</v>
@@ -24036,10 +24025,10 @@
         <v>248</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D253" s="4">
         <v>3</v>
@@ -24081,13 +24070,13 @@
         <v>-1</v>
       </c>
       <c r="Q253" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R253" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S253" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T253" s="7">
         <v>-1</v>
@@ -24126,10 +24115,10 @@
         <v>249</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D254" s="4">
         <v>3</v>
@@ -24171,13 +24160,13 @@
         <v>-1</v>
       </c>
       <c r="Q254" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R254" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S254" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T254" s="7">
         <v>-1</v>
@@ -24216,10 +24205,10 @@
         <v>250</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D255" s="4">
         <v>3</v>
@@ -24261,13 +24250,13 @@
         <v>-1</v>
       </c>
       <c r="Q255" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R255" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S255" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T255" s="7">
         <v>-1</v>
@@ -24306,10 +24295,10 @@
         <v>251</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D256" s="4">
         <v>3</v>
@@ -24351,13 +24340,13 @@
         <v>-1</v>
       </c>
       <c r="Q256" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="R256" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="S256" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="T256" s="7">
         <v>-1</v>
@@ -24396,16 +24385,16 @@
         <v>252</v>
       </c>
       <c r="B257" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C257" s="15" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D257" s="15">
         <v>10</v>
       </c>
       <c r="E257" s="59" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F257" s="16">
         <v>1</v>
@@ -24441,34 +24430,34 @@
         <v>130</v>
       </c>
       <c r="Q257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="R257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="S257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="T257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="U257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="V257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="W257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="X257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="Y257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="Z257" s="15" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AA257" s="15">
         <v>360000</v>
@@ -24486,10 +24475,10 @@
         <v>253</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D258" s="4">
         <v>5</v>
@@ -24531,19 +24520,19 @@
         <v>-1</v>
       </c>
       <c r="Q258" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="R258" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="S258" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="T258" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="U258" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="V258" s="7">
         <v>-1</v>
@@ -24576,10 +24565,10 @@
         <v>254</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D259" s="4">
         <v>5</v>
@@ -24621,19 +24610,19 @@
         <v>-1</v>
       </c>
       <c r="Q259" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="R259" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="S259" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="T259" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="U259" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="V259" s="7">
         <v>-1</v>
@@ -24666,10 +24655,10 @@
         <v>255</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D260" s="4">
         <v>5</v>
@@ -24711,19 +24700,19 @@
         <v>-1</v>
       </c>
       <c r="Q260" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="R260" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="S260" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="T260" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="U260" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="V260" s="7">
         <v>-1</v>
@@ -24756,16 +24745,16 @@
         <v>256</v>
       </c>
       <c r="B261" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D261" s="15">
         <v>10</v>
       </c>
       <c r="E261" s="59" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F261" s="16">
         <v>1</v>
@@ -24801,34 +24790,34 @@
         <v>220</v>
       </c>
       <c r="Q261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="R261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="S261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="T261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="U261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="V261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="W261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="X261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="Y261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="Z261" s="15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="AA261" s="15">
         <v>380000</v>
@@ -24846,10 +24835,10 @@
         <v>257</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D262" s="4">
         <v>3</v>
@@ -24891,13 +24880,13 @@
         <v>-1</v>
       </c>
       <c r="Q262" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="R262" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="S262" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="T262" s="7">
         <v>-1</v>
@@ -24936,16 +24925,16 @@
         <v>258</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D263" s="4">
         <v>3</v>
       </c>
       <c r="E263" s="64" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F263" s="11">
         <v>1</v>
@@ -24981,13 +24970,13 @@
         <v>-1</v>
       </c>
       <c r="Q263" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="R263" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="S263" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="T263" s="7">
         <v>-1</v>
@@ -25026,16 +25015,16 @@
         <v>259</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D264" s="4">
         <v>3</v>
       </c>
       <c r="E264" s="64" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F264" s="11">
         <v>0</v>
@@ -25071,13 +25060,13 @@
         <v>-1</v>
       </c>
       <c r="Q264" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="R264" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="S264" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="T264" s="7">
         <v>-1</v>
@@ -25116,10 +25105,10 @@
         <v>260</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D265" s="4">
         <v>3</v>
@@ -25161,13 +25150,13 @@
         <v>-1</v>
       </c>
       <c r="Q265" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="R265" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="S265" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="T265" s="7">
         <v>-1</v>
@@ -25206,16 +25195,16 @@
         <v>261</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C266" s="15" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D266" s="15">
         <v>10</v>
       </c>
       <c r="E266" s="59" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F266" s="16">
         <v>0</v>
@@ -25251,34 +25240,34 @@
         <v>160</v>
       </c>
       <c r="Q266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="R266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="S266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="T266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="U266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="V266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="W266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="X266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="Y266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="Z266" s="15" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="AA266" s="15">
         <v>400000</v>
@@ -25296,10 +25285,10 @@
         <v>262</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D267" s="4">
         <v>5</v>
@@ -25341,19 +25330,19 @@
         <v>-1</v>
       </c>
       <c r="Q267" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="R267" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="S267" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="T267" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="U267" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="V267" s="7">
         <v>-1</v>
@@ -25386,10 +25375,10 @@
         <v>263</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D268" s="4">
         <v>5</v>
@@ -25431,19 +25420,19 @@
         <v>-1</v>
       </c>
       <c r="Q268" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="R268" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="S268" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="T268" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="U268" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="V268" s="7">
         <v>-1</v>
@@ -25476,10 +25465,10 @@
         <v>264</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D269" s="4">
         <v>5</v>
@@ -25521,19 +25510,19 @@
         <v>-1</v>
       </c>
       <c r="Q269" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="R269" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="S269" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="T269" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="U269" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="V269" s="7">
         <v>-1</v>
@@ -25566,16 +25555,16 @@
         <v>265</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D270" s="6">
         <v>10</v>
       </c>
       <c r="E270" s="60" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F270" s="13">
         <v>0</v>
@@ -25611,34 +25600,34 @@
         <v>400</v>
       </c>
       <c r="Q270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="R270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="S270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="T270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="U270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="V270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="W270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="X270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="Y270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="Z270" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="AA270" s="6">
         <v>420000</v>
@@ -25656,10 +25645,10 @@
         <v>266</v>
       </c>
       <c r="B271" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C271" s="17" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D271" s="17">
         <v>5</v>
@@ -25701,19 +25690,19 @@
         <v>-1</v>
       </c>
       <c r="Q271" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="R271" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="S271" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="T271" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="U271" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="V271" s="7">
         <v>-1</v>
@@ -25746,10 +25735,10 @@
         <v>267</v>
       </c>
       <c r="B272" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C272" s="17" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D272" s="17">
         <v>5</v>
@@ -25791,19 +25780,19 @@
         <v>-1</v>
       </c>
       <c r="Q272" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="R272" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="S272" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="T272" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="U272" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="V272" s="7">
         <v>-1</v>
@@ -25836,10 +25825,10 @@
         <v>268</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C273" s="17" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D273" s="17">
         <v>5</v>
@@ -25881,19 +25870,19 @@
         <v>-1</v>
       </c>
       <c r="Q273" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="R273" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="S273" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="T273" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="U273" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="V273" s="7">
         <v>-1</v>
@@ -25926,16 +25915,16 @@
         <v>269</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D274" s="6">
         <v>10</v>
       </c>
       <c r="E274" s="60" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F274" s="13">
         <v>0</v>
@@ -25971,34 +25960,34 @@
         <v>200</v>
       </c>
       <c r="Q274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="R274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="S274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="T274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="U274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="V274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="W274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="X274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="Y274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="Z274" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="AA274" s="6">
         <v>440000</v>
@@ -26016,10 +26005,10 @@
         <v>270</v>
       </c>
       <c r="B275" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C275" s="17" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D275" s="17">
         <v>3</v>
@@ -26061,13 +26050,13 @@
         <v>-1</v>
       </c>
       <c r="Q275" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="R275" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="S275" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="T275" s="7">
         <v>-1</v>
@@ -26106,10 +26095,10 @@
         <v>271</v>
       </c>
       <c r="B276" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C276" s="17" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D276" s="17">
         <v>3</v>
@@ -26151,13 +26140,13 @@
         <v>-1</v>
       </c>
       <c r="Q276" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="R276" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="S276" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="T276" s="7">
         <v>-1</v>
@@ -26196,10 +26185,10 @@
         <v>272</v>
       </c>
       <c r="B277" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C277" s="17" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D277" s="17">
         <v>3</v>
@@ -26241,13 +26230,13 @@
         <v>-1</v>
       </c>
       <c r="Q277" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="R277" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="S277" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="T277" s="7">
         <v>-1</v>
@@ -26286,10 +26275,10 @@
         <v>273</v>
       </c>
       <c r="B278" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C278" s="17" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D278" s="17">
         <v>3</v>
@@ -26331,13 +26320,13 @@
         <v>-1</v>
       </c>
       <c r="Q278" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="R278" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="S278" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="T278" s="7">
         <v>-1</v>
@@ -26376,16 +26365,16 @@
         <v>274</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D279" s="6">
         <v>10</v>
       </c>
       <c r="E279" s="60" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F279" s="13">
         <v>1</v>
@@ -26421,34 +26410,34 @@
         <v>240</v>
       </c>
       <c r="Q279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="R279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="S279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="T279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="U279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="W279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="X279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="Y279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="Z279" s="6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="AA279" s="6">
         <v>460000</v>
@@ -26466,16 +26455,16 @@
         <v>275</v>
       </c>
       <c r="B280" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C280" s="17" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D280" s="17">
         <v>5</v>
       </c>
       <c r="E280" s="61" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F280" s="18">
         <v>0</v>
@@ -26511,19 +26500,19 @@
         <v>-1</v>
       </c>
       <c r="Q280" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="R280" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="S280" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="T280" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="U280" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="V280" s="7">
         <v>-1</v>
@@ -26556,10 +26545,10 @@
         <v>276</v>
       </c>
       <c r="B281" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C281" s="17" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D281" s="17">
         <v>5</v>
@@ -26601,19 +26590,19 @@
         <v>-1</v>
       </c>
       <c r="Q281" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="R281" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="S281" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="T281" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="U281" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="V281" s="7">
         <v>-1</v>
@@ -26646,10 +26635,10 @@
         <v>277</v>
       </c>
       <c r="B282" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C282" s="17" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D282" s="17">
         <v>5</v>
@@ -26691,19 +26680,19 @@
         <v>-1</v>
       </c>
       <c r="Q282" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="R282" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="S282" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="T282" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="U282" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="V282" s="7">
         <v>-1</v>
@@ -26736,10 +26725,10 @@
         <v>278</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D283" s="6">
         <v>3</v>
@@ -26781,13 +26770,13 @@
         <v>-1</v>
       </c>
       <c r="Q283" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="R283" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="S283" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="T283" s="7">
         <v>-1</v>
@@ -26826,10 +26815,10 @@
         <v>279</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D284" s="6">
         <v>3</v>
@@ -26871,13 +26860,13 @@
         <v>-1</v>
       </c>
       <c r="Q284" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="R284" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="S284" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="T284" s="7">
         <v>-1</v>
@@ -26916,10 +26905,10 @@
         <v>280</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D285" s="6">
         <v>3</v>
@@ -26961,13 +26950,13 @@
         <v>-1</v>
       </c>
       <c r="Q285" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="R285" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="S285" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="T285" s="7">
         <v>-1</v>
@@ -27006,10 +26995,10 @@
         <v>281</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D286" s="6">
         <v>3</v>
@@ -27051,13 +27040,13 @@
         <v>-1</v>
       </c>
       <c r="Q286" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="R286" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="S286" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="T286" s="7">
         <v>-1</v>
@@ -27096,10 +27085,10 @@
         <v>282</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D287" s="6">
         <v>3</v>
@@ -27141,13 +27130,13 @@
         <v>-1</v>
       </c>
       <c r="Q287" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="R287" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="S287" s="6" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="T287" s="7">
         <v>-1</v>
@@ -27186,16 +27175,16 @@
         <v>283</v>
       </c>
       <c r="B288" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C288" s="17" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D288" s="17">
         <v>3</v>
       </c>
       <c r="E288" s="61" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F288" s="18">
         <v>0</v>
@@ -27231,13 +27220,13 @@
         <v>-1</v>
       </c>
       <c r="Q288" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="R288" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="S288" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="T288" s="7">
         <v>-1</v>
@@ -27276,10 +27265,10 @@
         <v>284</v>
       </c>
       <c r="B289" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C289" s="17" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D289" s="17">
         <v>3</v>
@@ -27321,13 +27310,13 @@
         <v>-1</v>
       </c>
       <c r="Q289" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="R289" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="S289" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="T289" s="7">
         <v>-1</v>
@@ -27366,10 +27355,10 @@
         <v>285</v>
       </c>
       <c r="B290" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C290" s="17" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D290" s="17">
         <v>3</v>
@@ -27411,13 +27400,13 @@
         <v>-1</v>
       </c>
       <c r="Q290" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="R290" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="S290" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="T290" s="7">
         <v>-1</v>
@@ -27456,10 +27445,10 @@
         <v>286</v>
       </c>
       <c r="B291" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C291" s="17" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D291" s="17">
         <v>3</v>
@@ -27501,13 +27490,13 @@
         <v>-1</v>
       </c>
       <c r="Q291" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="R291" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="S291" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="T291" s="7">
         <v>-1</v>
@@ -27546,16 +27535,16 @@
         <v>287</v>
       </c>
       <c r="B292" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C292" s="17" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D292" s="17">
         <v>3</v>
       </c>
       <c r="E292" s="61" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F292" s="18">
         <v>0</v>
@@ -27591,13 +27580,13 @@
         <v>-1</v>
       </c>
       <c r="Q292" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="R292" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="S292" s="17" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="T292" s="7">
         <v>-1</v>
@@ -27636,10 +27625,10 @@
         <v>288</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D293" s="6">
         <v>3</v>
@@ -27681,13 +27670,13 @@
         <v>-1</v>
       </c>
       <c r="Q293" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="R293" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="S293" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="T293" s="7">
         <v>-1</v>
@@ -27726,10 +27715,10 @@
         <v>289</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D294" s="6">
         <v>3</v>
@@ -27771,13 +27760,13 @@
         <v>-1</v>
       </c>
       <c r="Q294" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="R294" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="S294" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="T294" s="7">
         <v>-1</v>
@@ -27816,10 +27805,10 @@
         <v>290</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D295" s="6">
         <v>3</v>
@@ -27861,13 +27850,13 @@
         <v>-1</v>
       </c>
       <c r="Q295" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="R295" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="S295" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="T295" s="7">
         <v>-1</v>
@@ -27906,10 +27895,10 @@
         <v>291</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D296" s="6">
         <v>3</v>
@@ -27951,13 +27940,13 @@
         <v>-1</v>
       </c>
       <c r="Q296" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="R296" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="S296" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="T296" s="7">
         <v>-1</v>
@@ -27996,10 +27985,10 @@
         <v>292</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D297" s="6">
         <v>3</v>
@@ -28041,13 +28030,13 @@
         <v>-1</v>
       </c>
       <c r="Q297" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="R297" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="S297" s="6" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="T297" s="7">
         <v>-1</v>
@@ -28086,10 +28075,10 @@
         <v>293</v>
       </c>
       <c r="B298" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C298" s="17" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D298" s="17">
         <v>5</v>
@@ -28131,19 +28120,19 @@
         <v>-1</v>
       </c>
       <c r="Q298" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="R298" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="S298" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="T298" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="U298" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="V298" s="7">
         <v>-1</v>
@@ -28176,16 +28165,16 @@
         <v>294</v>
       </c>
       <c r="B299" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C299" s="17" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D299" s="17">
         <v>5</v>
       </c>
       <c r="E299" s="61" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F299" s="18">
         <v>1</v>
@@ -28221,19 +28210,19 @@
         <v>-1</v>
       </c>
       <c r="Q299" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="R299" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="S299" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="T299" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="U299" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="V299" s="7">
         <v>-1</v>
@@ -28266,16 +28255,16 @@
         <v>295</v>
       </c>
       <c r="B300" s="17" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C300" s="17" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D300" s="17">
         <v>5</v>
       </c>
       <c r="E300" s="61" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F300" s="18">
         <v>0</v>
@@ -28311,19 +28300,19 @@
         <v>-1</v>
       </c>
       <c r="Q300" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="R300" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="S300" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="T300" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="U300" s="17" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="V300" s="7">
         <v>-1</v>
